--- a/public/documents/pieces-reponse-1/R1-degustations-par-note.xlsx
+++ b/public/documents/pieces-reponse-1/R1-degustations-par-note.xlsx
@@ -122,6 +122,9 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -136,9 +139,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,11 +504,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -516,6 +516,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,40 +541,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>Conditionnement d’achat</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>Exercice 1 (2022-2023) : notes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Exercice 1 (2022-2023) : litres</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Exercice 2 (2023-2024) : notes</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Exercice 2 (2023-2024) : litres</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Exercice 3 (2024-2025) : notes</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Exercice 3 (2024-2025) : litres</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>3 exercices : notes</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>3 exercices : litres</t>
         </is>
@@ -585,28 +591,33 @@
           <t>Savagnin</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>531</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="D4" s="6" t="n">
         <v>10.62</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="E4" s="5" t="n">
         <v>475</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <v>484</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="6" t="n">
         <v>9.68</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>1490</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>29.8</v>
       </c>
     </row>
@@ -616,28 +627,33 @@
           <t>Arbois Trousseau</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>333</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="D5" s="6" t="n">
         <v>6.66</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="E5" s="5" t="n">
         <v>316</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>6.32</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>5.94</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>946</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>18.92</v>
       </c>
     </row>
@@ -647,370 +663,557 @@
           <t>Saint Véran</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>243</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="D6" s="6" t="n">
         <v>4.86</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="E6" s="5" t="n">
         <v>249</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>4.98</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>273</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="6" t="n">
         <v>5.46</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>765</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>15.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Aligoté</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>285</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>303</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>588</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>11.76</v>
+          <t>HC de Beaune</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>454</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>9.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Chusclan</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>268</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>236</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>504</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>10.08</v>
+          <t>Moulin à Vent</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>446</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>8.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>HC de Beaune</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>454</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>9.08</v>
+          <t>Mâcon</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>6.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Moulin à Vent</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>446</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>8.92</v>
+          <t>Gewurztraminer</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>5.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mâcon</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>179</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>346</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>6.92</v>
+          <t>Arbois Chardonnay</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>4.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Gewurztraminer</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>5.58</v>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>3.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arbois Chardonnay</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F13" s="5" t="n">
+          <t>Saint Joseph</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I13" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>233</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>4.66</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Chablis</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3.02</v>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total bouteilles bouchées (volume demandé)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bouteille bouchée 75 cl</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1768</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1704</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1728</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>5200</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Saint Joseph</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>1.8</v>
+          <t>Aligoté</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>BIB 10 L</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>303</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>588</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>11.76</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Chusclan</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>BIB 10 L</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>504</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total BIB de 10 L (retiré de la demande)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>BIB 10 L</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>553</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>539</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>1092</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>21.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Les douze vins nommés</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>1768</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="D18" s="9" t="n">
         <v>35.36</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="E18" s="8" t="n">
         <v>2257</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="F18" s="9" t="n">
         <v>45.14</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="G18" s="8" t="n">
         <v>2267</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="H18" s="9" t="n">
         <v>45.34</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="I18" s="8" t="n">
         <v>6292</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="J18" s="9" t="n">
         <v>125.84</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Lignes de vin nommé lues en caisse (verre / pichet)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>6326</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Notes (additions) distinctes concernées, 3 exercices</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5457</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Lignes de vin nommé lues en caisse (verre / pichet)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6326</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notes (additions) distinctes concernées, 3 exercices</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Dose retenue par dégustation</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2 cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Vins achetés en BIB de 10 L (Aligoté, Chusclan)</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>1 092 dégustations, soit 21,84 L : volume RETIRÉ de la demande, couvert par l’abattement « vins au BIB » (198 L) du service</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vins achetés en bouteille bouchée de 75 cl (les dix autres)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>5 200 dégustations, soit 104,00 L : volume DEMANDÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Volume demandé au titre de la dégustation offerte</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>104,00 L sur les 125,84 L comptés</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Source du conditionnement</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Champ « unite_achat » de src/data/calculsBoissons/consoTotaleParBoisson.json, renseigné d’après les factures du fournisseur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fait de service restant à attester</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Le décompte relève un geste de service et lui applique 2 cl. Que cette larme soit versée dans un verre distinct, et s’ajoute donc à la dose vendue au lieu de s’imputer sur elle, est un point de pratique que la société doit attester : la présente pièce ne l’établit pas.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1228,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,10 +1272,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>dont vins achetés en BIB de 10 L (L), retirés de la demande</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>dont vins en bouteille bouchée de 75 cl (L), volume demandé</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>Abattement 15 % BIB annoncé par le service (L)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Abattement 15 % bouteilles annoncé par le service (L)</t>
         </is>
@@ -1089,9 +1304,15 @@
         <v>35.36</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <v>175.35</v>
       </c>
     </row>
@@ -1108,9 +1329,15 @@
         <v>45.14</v>
       </c>
       <c r="D5" s="5" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>66.12</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>173.08</v>
       </c>
     </row>
@@ -1127,9 +1354,15 @@
         <v>45.34</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>153.11</v>
       </c>
     </row>
@@ -1146,45 +1379,75 @@
         <v>125.84</v>
       </c>
       <c r="D7" s="7" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <v>198.15</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="G7" s="7" t="n">
         <v>501.54</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Périmètre du décompte de dégustation</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Vins nommés servis au verre ou au pichet, versés depuis une bouteille.</t>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Vins nommés servis au verre ou au pichet. Dix d’entre eux sont achetés en bouteille bouchée de 75 cl ; deux, le Bourgogne Aligoté maison et le Côtes du Rhône rouge maison de Chusclan, sont achetés en BIB de 10 L.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Périmètre exclu du décompte</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Génériques « Verre de vin » / « Pichet vin » (cubis, c’est-à-dire le BIB) et bouteilles vendues entières.</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Génériques « Verre de vin » / « Pichet vin » (cubis, type non précisé) et bouteilles vendues entières.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Conséquence</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>L’abattement de 15 % « vins au BIB » (198 L) porte exactement sur le périmètre que le décompte exclut : les deux volumes ne se recouvrent pas.</t>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Conséquence, part couverte par l’abattement « vins au BIB »</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Les 1 092 dégustations d’Aligoté et de Chusclan, soit 21,84 L, relèvent du périmètre auquel le service applique son abattement de 198 L : elles sont retirées de la demande.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Conséquence, part non couverte</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Les 104,00 L restants portent sur des vins en bouteille bouchée. Le service leur oppose son second abattement de 15 %, celui dont il affecte par ailleurs l’intégralité aux offerts, aux pertes et à la consommation du personnel (onglet « Double emploi 15 % »).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Volume demandé au titre de la dégustation offerte</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>104,00 L sur les 125,84 L comptés.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1552,7 @@
       <c r="F4" s="5" t="n">
         <v>68.1495</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="11" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -1449,56 +1712,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Vins au BIB</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Cumul 3 exercices</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Somme des 3 lignes ci-dessus</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
-      <c r="E11" s="12" t="n">
+      <c r="D11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="n">
         <v>198</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="13" t="n">
         <v>198.15</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Vins bouteilles bouchées</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Cumul 3 exercices</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Somme des 3 lignes ci-dessus</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="n">
+      <c r="D12" s="13" t="inlineStr"/>
+      <c r="E12" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="13" t="n">
         <v>501.54</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="13" t="n">
         <v>1.54</v>
       </c>
     </row>
@@ -1537,232 +1800,232 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Poste de perte en discussion</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Ce que le service oppose</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Citation du courrier</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>p. 61</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Freinte technique de la bière (mousse, collerette, nettoyage des lignes, fond de fût)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Le taux de 15 % de fin de méthode, cumulé avec un taux spécifique de 15 % sur la bière</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>« le service, compte tenu de la méthode de reconstitution employée, applique, en fin de méthode, 15 %, supplémentaires en taux de perte/offert/consommation du personnel » ; « le service retient donc en fait, un taux total de 30 % sur la bière »</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>p. 72</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Offerts commerciaux</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>La tranche de 5 % « offerts », comprise dans le 15 %</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>« La réponse n’apporte aucun élément pertinent susceptible de considérer que les offerts, les pertes et les consommations du personnel pourraient être supérieurs aux 15 % retenus par le service. » ; « avec la proportion de 5 % pour l’offert, le service a minoré le montant du chiffre d’affaires TTC reconstitué, sur le premier exercice à hauteur de 35 133,26 € »</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>p. 72</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Pertes et casse</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>La tranche de 5 % « pertes », comprise dans le 15 %</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>« avec la proportion de 5 % pour les pertes, le service minore le montant du chiffre d’affaires TTC reconstitué à hauteur de 35 133,26 € »</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>p. 73</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Consommation du personnel</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>La tranche de 5 % « consommation du personnel », comprise dans le 15 %</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>« le taux de 5 % appliqué pour la consommation du personnel, impacte toutes les boissons, y compris celles alcoolisées » ; « avec la proportion de 5 % pour la consommation du personnel, service a minoré le montant du chiffre d’affaires TTC reconstitué, sur le premier exercice à hauteur de 35 133,26 € »</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>p. 83</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Freinte technique de la bière (à nouveau)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Le même 15 % de fin de méthode, additionné au 15 % interne à la méthode</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>« en fin de reconstitution, le service applique bien un taux de 15 % pour pertes, offerts et consommations du personnel. Mais, à l’intérieur de la méthode de reconstitution, le service avait, auparavant, déjà appliqué un taux spécifique sur perte de bière de 15 %. » ; « en cumulant les deux taux de sa méthode de reconstitution, le service avait déjà appliqué un taux de pertes, offerts, consommation du personnel de 30 % »</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>p. 64 et p. 86</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Dégustation offerte (goûter du vin)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Le même 15 %, appliqué cette fois au volume de vin disponible (198 L au BIB, 500 L en bouteilles)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>« le service a déjà retenu un taux offert/perte/consommation du personnel de 15 % (en fin de méthode de reconstitution) » ; « le cumul de 500 litres (arrondis) sur les trois exercices est près de 4 fois supérieur aux 125,80 litres proposées par Maître THIVEND »</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>p. 89</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Dégustation offerte (à nouveau)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Les trois mêmes tranches de 5 %, chiffrées aux mêmes 35 133,26 € par exercice</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>« en retenant un taux de 5 % d’offerts dans sa méthode de reconstitution, a minoré le montant du chiffre d’affaires TTC reconstitué, sur le premier exercice à hauteur de 35 133,26 € » ; « avec une proportion de 5 % pour les pertes, le service minore […] 35 133,26 €, pour un exercice » ; « Avec la proportion de 5 % pour la consommation du personnel, service a minoré […] 35 133,26 € »</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>p. 93</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Vraisemblance du coefficient multiplicateur</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Le même 15 %, cette fois utilisé une seule fois (et non 30 %) pour justifier le coefficient</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>« grâce aux taux de perte/offerts/consommation du personnel de 15 %, retenu par le service, le coefficient moyen de l’exploitation de la société devrait être de : 3,85 x (1-0,15) = 3,2725 »</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>p. 62 et p. 63</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Crémant jeté</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Aucun abattement opposé : le service conteste le principe même de la perte</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Ces deux pages n’invoquent aucun taux d’abattement pour pertes : le forfait de 15 % n’y est pas mentionné.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Un taux unique de 15 %, appliqué une seule fois en fin de reconstitution, est opposé successivement à plusieurs postes de perte distincts. Chacun de ces postes ne peut être réputé « déjà couvert » par la totalité du même taux.</t>
         </is>
